--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G972"/>
+  <dimension ref="A1:G973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26680,6 +26680,33 @@
         <v>223.96</v>
       </c>
       <c r="G972" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>253</v>
+      </c>
+      <c r="C973" t="n">
+        <v>226.75</v>
+      </c>
+      <c r="D973" t="n">
+        <v>233.61</v>
+      </c>
+      <c r="E973" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="F973" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="G973" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26696,7 +26723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1055"/>
+  <dimension ref="A1:B1056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37249,6 +37276,16 @@
       </c>
       <c r="B1055" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -37411,28 +37448,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5841769092013344</v>
+        <v>0.5849766877226318</v>
       </c>
       <c r="J2" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K2" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08992130414329691</v>
+        <v>0.09032902153924915</v>
       </c>
       <c r="M2" t="n">
-        <v>9.89682954964522</v>
+        <v>9.892723394130321</v>
       </c>
       <c r="N2" t="n">
-        <v>190.6136025410289</v>
+        <v>190.4327435081098</v>
       </c>
       <c r="O2" t="n">
-        <v>13.80628851433393</v>
+        <v>13.79973708112259</v>
       </c>
       <c r="P2" t="n">
-        <v>233.7157612434608</v>
+        <v>233.7075123897593</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37483,28 +37520,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04303444445868781</v>
+        <v>0.04336500373592209</v>
       </c>
       <c r="J3" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K3" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01455193984057601</v>
+        <v>0.01480128942767389</v>
       </c>
       <c r="M3" t="n">
-        <v>2.246395128339956</v>
+        <v>2.245691372526549</v>
       </c>
       <c r="N3" t="n">
-        <v>6.921401063302737</v>
+        <v>6.916884639007425</v>
       </c>
       <c r="O3" t="n">
-        <v>2.630855576291244</v>
+        <v>2.629997079657585</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0216111090272</v>
+        <v>224.0182017462537</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37555,28 +37592,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1279164283448089</v>
+        <v>0.1284205539715788</v>
       </c>
       <c r="J4" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K4" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1402456429056597</v>
+        <v>0.1413449960960356</v>
       </c>
       <c r="M4" t="n">
-        <v>1.990346098069382</v>
+        <v>1.9909716159313</v>
       </c>
       <c r="N4" t="n">
-        <v>5.535876873943448</v>
+        <v>5.536238835234291</v>
       </c>
       <c r="O4" t="n">
-        <v>2.352844421958972</v>
+        <v>2.352921340638971</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7964563773969</v>
+        <v>227.7912568647422</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37627,28 +37664,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1146014392666247</v>
+        <v>0.1150571384090308</v>
       </c>
       <c r="J5" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K5" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07470637654754331</v>
+        <v>0.07537973854200453</v>
       </c>
       <c r="M5" t="n">
-        <v>2.46828792261165</v>
+        <v>2.468115744461028</v>
       </c>
       <c r="N5" t="n">
-        <v>8.977404746213338</v>
+        <v>8.97311820109503</v>
       </c>
       <c r="O5" t="n">
-        <v>2.996231757760627</v>
+        <v>2.995516349662447</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8711406983256</v>
+        <v>218.8664406526785</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37699,28 +37736,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2485790874518768</v>
+        <v>0.2485442170558543</v>
       </c>
       <c r="J6" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K6" t="n">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3107620992084179</v>
+        <v>0.3111973686908616</v>
       </c>
       <c r="M6" t="n">
-        <v>2.259822579644198</v>
+        <v>2.257666178863433</v>
       </c>
       <c r="N6" t="n">
-        <v>7.56343446953634</v>
+        <v>7.555682139519863</v>
       </c>
       <c r="O6" t="n">
-        <v>2.750169898303801</v>
+        <v>2.748760109489343</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9055276808506</v>
+        <v>216.9058873314134</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37758,7 +37795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G972"/>
+  <dimension ref="A1:G973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73725,6 +73762,43 @@
         </is>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>-41.042877615840304,173.02023708559372</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>-41.042408444143916,173.01945001669586</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>-41.041823588671576,173.01904422247713</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>-41.04118608063109,173.01858592187614</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>-41.04051958962748,173.01822393079624</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G973"/>
+  <dimension ref="A1:G974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26709,6 +26709,33 @@
       <c r="G973" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="C974" t="n">
+        <v>226.92</v>
+      </c>
+      <c r="D974" t="n">
+        <v>233.95</v>
+      </c>
+      <c r="E974" t="n">
+        <v>223.83</v>
+      </c>
+      <c r="F974" t="n">
+        <v>223.45</v>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26723,7 +26750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1056"/>
+  <dimension ref="A1:B1057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37286,6 +37313,16 @@
       </c>
       <c r="B1056" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -37448,28 +37485,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5849766877226318</v>
+        <v>0.5860999225063994</v>
       </c>
       <c r="J2" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K2" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09032902153924915</v>
+        <v>0.09082267800681532</v>
       </c>
       <c r="M2" t="n">
-        <v>9.892723394130321</v>
+        <v>9.891066458335109</v>
       </c>
       <c r="N2" t="n">
-        <v>190.4327435081098</v>
+        <v>190.2671491984787</v>
       </c>
       <c r="O2" t="n">
-        <v>13.79973708112259</v>
+        <v>13.79373586808442</v>
       </c>
       <c r="P2" t="n">
-        <v>233.7075123897593</v>
+        <v>233.6959165012576</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37520,28 +37557,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04336500373592209</v>
+        <v>0.04372836979665991</v>
       </c>
       <c r="J3" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K3" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01480128942767389</v>
+        <v>0.01507419860619741</v>
       </c>
       <c r="M3" t="n">
-        <v>2.245691372526549</v>
+        <v>2.245144919115293</v>
       </c>
       <c r="N3" t="n">
-        <v>6.916884639007425</v>
+        <v>6.912928227701475</v>
       </c>
       <c r="O3" t="n">
-        <v>2.629997079657585</v>
+        <v>2.629244801782724</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0182017462537</v>
+        <v>224.0144504803683</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37592,28 +37629,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1284205539715788</v>
+        <v>0.1289935197704701</v>
       </c>
       <c r="J4" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K4" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1413449960960356</v>
+        <v>0.1425388146517975</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9909716159313</v>
+        <v>1.991971785408537</v>
       </c>
       <c r="N4" t="n">
-        <v>5.536238835234291</v>
+        <v>5.538387084239782</v>
       </c>
       <c r="O4" t="n">
-        <v>2.352921340638971</v>
+        <v>2.353377803124646</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7912568647422</v>
+        <v>227.7853417634515</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37664,28 +37701,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1150571384090308</v>
+        <v>0.1154545143295844</v>
       </c>
       <c r="J5" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K5" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07537973854200453</v>
+        <v>0.07599465983360654</v>
       </c>
       <c r="M5" t="n">
-        <v>2.468115744461028</v>
+        <v>2.467637341769895</v>
       </c>
       <c r="N5" t="n">
-        <v>8.97311820109503</v>
+        <v>8.967666224088228</v>
       </c>
       <c r="O5" t="n">
-        <v>2.995516349662447</v>
+        <v>2.994606188480921</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8664406526785</v>
+        <v>218.8623382807305</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37736,28 +37773,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2485442170558543</v>
+        <v>0.2485379458666397</v>
       </c>
       <c r="J6" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="K6" t="n">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3111973686908616</v>
+        <v>0.3116829130611555</v>
       </c>
       <c r="M6" t="n">
-        <v>2.257666178863433</v>
+        <v>2.255376078971689</v>
       </c>
       <c r="N6" t="n">
-        <v>7.555682139519863</v>
+        <v>7.547917731999915</v>
       </c>
       <c r="O6" t="n">
-        <v>2.748760109489343</v>
+        <v>2.747347399219821</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9058873314134</v>
+        <v>216.9059520730079</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37795,7 +37832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G973"/>
+  <dimension ref="A1:G974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73799,6 +73836,43 @@
         </is>
       </c>
     </row>
+    <row r="974">
+      <c r="A974" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>-41.04286963439433,173.02025293716892</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>-41.04240759612682,173.01945170092407</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>-41.04182245289789,173.01904797933986</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>-41.04118698333689,173.01858293891902</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>-41.04051908840074,173.01822558812384</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G974"/>
+  <dimension ref="A1:G976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26736,6 +26736,60 @@
       <c r="G974" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:42+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>254.95</v>
+      </c>
+      <c r="C975" t="n">
+        <v>226.17</v>
+      </c>
+      <c r="D975" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="E975" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="F975" t="n">
+        <v>222.15</v>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>251.43</v>
+      </c>
+      <c r="C976" t="n">
+        <v>226.15</v>
+      </c>
+      <c r="D976" t="n">
+        <v>233.37</v>
+      </c>
+      <c r="E976" t="n">
+        <v>222.37</v>
+      </c>
+      <c r="F976" t="n">
+        <v>222.07</v>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1057"/>
+  <dimension ref="A1:B1059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37323,6 +37377,26 @@
       </c>
       <c r="B1057" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
@@ -37485,28 +37559,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5860999225063994</v>
+        <v>0.5877356608826144</v>
       </c>
       <c r="J2" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="K2" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09082267800681532</v>
+        <v>0.09165621805074864</v>
       </c>
       <c r="M2" t="n">
-        <v>9.891066458335109</v>
+        <v>9.883060886709385</v>
       </c>
       <c r="N2" t="n">
-        <v>190.2671491984787</v>
+        <v>189.9149675329346</v>
       </c>
       <c r="O2" t="n">
-        <v>13.79373586808442</v>
+        <v>13.78096395514242</v>
       </c>
       <c r="P2" t="n">
-        <v>233.6959165012576</v>
+        <v>233.6789635587827</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37557,28 +37631,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04372836979665991</v>
+        <v>0.0441372277455969</v>
       </c>
       <c r="J3" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="K3" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01507419860619741</v>
+        <v>0.015419608646139</v>
       </c>
       <c r="M3" t="n">
-        <v>2.245144919115293</v>
+        <v>2.242500210531125</v>
       </c>
       <c r="N3" t="n">
-        <v>6.912928227701475</v>
+        <v>6.900725129325801</v>
       </c>
       <c r="O3" t="n">
-        <v>2.629244801782724</v>
+        <v>2.626923129694853</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0144504803683</v>
+        <v>224.0102120638467</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37629,28 +37703,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1289935197704701</v>
+        <v>0.1298761885940856</v>
       </c>
       <c r="J4" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="K4" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1425388146517975</v>
+        <v>0.1445862334544586</v>
       </c>
       <c r="M4" t="n">
-        <v>1.991971785408537</v>
+        <v>1.992542927360306</v>
       </c>
       <c r="N4" t="n">
-        <v>5.538387084239782</v>
+        <v>5.536243149005755</v>
       </c>
       <c r="O4" t="n">
-        <v>2.353377803124646</v>
+        <v>2.352922257322956</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7853417634515</v>
+        <v>227.7761914675743</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37701,28 +37775,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1154545143295844</v>
+        <v>0.1156673704528776</v>
       </c>
       <c r="J5" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="K5" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07599465983360654</v>
+        <v>0.07657972479344755</v>
       </c>
       <c r="M5" t="n">
-        <v>2.467637341769895</v>
+        <v>2.463666669209554</v>
       </c>
       <c r="N5" t="n">
-        <v>8.967666224088228</v>
+        <v>8.949816365241125</v>
       </c>
       <c r="O5" t="n">
-        <v>2.994606188480921</v>
+        <v>2.991624369007768</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8623382807305</v>
+        <v>218.8601318534838</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37773,28 +37847,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2485379458666397</v>
+        <v>0.2479616296670242</v>
       </c>
       <c r="J6" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="K6" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3116829130611555</v>
+        <v>0.3115788523082943</v>
       </c>
       <c r="M6" t="n">
-        <v>2.255376078971689</v>
+        <v>2.253495905207782</v>
       </c>
       <c r="N6" t="n">
-        <v>7.547917731999915</v>
+        <v>7.536366116232895</v>
       </c>
       <c r="O6" t="n">
-        <v>2.747347399219821</v>
+        <v>2.745244272598141</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9059520730079</v>
+        <v>216.9119265628481</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37832,7 +37906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G974"/>
+  <dimension ref="A1:G976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73873,6 +73947,80 @@
         </is>
       </c>
     </row>
+    <row r="975">
+      <c r="A975" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:13:42+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>-41.04286788845273,173.0202564047005</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>-41.04241133737854,173.01944427050523</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>-41.041824624229825,173.0190407971022</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>-41.04119142999764,173.01856824509204</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>-41.04052343236501,173.01821122461712</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-17 22:07:34+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>-41.04288544763203,173.0202215312318</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>-41.04241143714524,173.01944407236073</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>-41.041824390394105,173.019041570574</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>-41.04119186463356,173.0185668088532</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>-41.04052369968584,173.01821034070895</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G976"/>
+  <dimension ref="A1:G980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26788,6 +26788,114 @@
         <v>222.07</v>
       </c>
       <c r="G976" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>250.01</v>
+      </c>
+      <c r="C977" t="n">
+        <v>225.48</v>
+      </c>
+      <c r="D977" t="n">
+        <v>232.54</v>
+      </c>
+      <c r="E977" t="n">
+        <v>221.36</v>
+      </c>
+      <c r="F977" t="n">
+        <v>221.75</v>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>250.62</v>
+      </c>
+      <c r="C978" t="n">
+        <v>225.07</v>
+      </c>
+      <c r="D978" t="n">
+        <v>232.39</v>
+      </c>
+      <c r="E978" t="n">
+        <v>220.86</v>
+      </c>
+      <c r="F978" t="n">
+        <v>221.17</v>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>248.2</v>
+      </c>
+      <c r="C979" t="n">
+        <v>224.01</v>
+      </c>
+      <c r="D979" t="n">
+        <v>231.27</v>
+      </c>
+      <c r="E979" t="n">
+        <v>219.9</v>
+      </c>
+      <c r="F979" t="n">
+        <v>220.12</v>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>244.49</v>
+      </c>
+      <c r="C980" t="n">
+        <v>223.94</v>
+      </c>
+      <c r="D980" t="n">
+        <v>231.26</v>
+      </c>
+      <c r="E980" t="n">
+        <v>219.86</v>
+      </c>
+      <c r="F980" t="n">
+        <v>220.11</v>
+      </c>
+      <c r="G980" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26804,7 +26912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1059"/>
+  <dimension ref="A1:B1063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37397,6 +37505,46 @@
       </c>
       <c r="B1059" t="n">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>
@@ -37559,28 +37707,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5877356608826144</v>
+        <v>0.5869226719078113</v>
       </c>
       <c r="J2" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="K2" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09165621805074864</v>
+        <v>0.09219321485729204</v>
       </c>
       <c r="M2" t="n">
-        <v>9.883060886709385</v>
+        <v>9.848775466821383</v>
       </c>
       <c r="N2" t="n">
-        <v>189.9149675329346</v>
+        <v>189.1664720566333</v>
       </c>
       <c r="O2" t="n">
-        <v>13.78096395514242</v>
+        <v>13.75378028240357</v>
       </c>
       <c r="P2" t="n">
-        <v>233.6789635587827</v>
+        <v>233.6874346327299</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37631,28 +37779,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0441372277455969</v>
+        <v>0.04367660491374936</v>
       </c>
       <c r="J3" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="K3" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="L3" t="n">
-        <v>0.015419608646139</v>
+        <v>0.01523726994646768</v>
       </c>
       <c r="M3" t="n">
-        <v>2.242500210531125</v>
+        <v>2.236267136486437</v>
       </c>
       <c r="N3" t="n">
-        <v>6.900725129325801</v>
+        <v>6.875592259739072</v>
       </c>
       <c r="O3" t="n">
-        <v>2.626923129694853</v>
+        <v>2.622135057494002</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0102120638467</v>
+        <v>224.0150062607071</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37703,28 +37851,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1298761885940856</v>
+        <v>0.1303973920187286</v>
       </c>
       <c r="J4" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="K4" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1445862334544586</v>
+        <v>0.1466754379547395</v>
       </c>
       <c r="M4" t="n">
-        <v>1.992542927360306</v>
+        <v>1.987150821290527</v>
       </c>
       <c r="N4" t="n">
-        <v>5.536243149005755</v>
+        <v>5.516740951029801</v>
       </c>
       <c r="O4" t="n">
-        <v>2.352922257322956</v>
+        <v>2.348774350811461</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7761914675743</v>
+        <v>227.7707783374848</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37775,28 +37923,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1156673704528776</v>
+        <v>0.1144774580889094</v>
       </c>
       <c r="J5" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="K5" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07657972479344755</v>
+        <v>0.07570282387871829</v>
       </c>
       <c r="M5" t="n">
-        <v>2.463666669209554</v>
+        <v>2.459200352490003</v>
       </c>
       <c r="N5" t="n">
-        <v>8.949816365241125</v>
+        <v>8.923339753069115</v>
       </c>
       <c r="O5" t="n">
-        <v>2.991624369007768</v>
+        <v>2.98719596830692</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8601318534838</v>
+        <v>218.8725072544698</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37847,28 +37995,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2479616296670242</v>
+        <v>0.2457185611822711</v>
       </c>
       <c r="J6" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="K6" t="n">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3115788523082943</v>
+        <v>0.3087821704936267</v>
       </c>
       <c r="M6" t="n">
-        <v>2.253495905207782</v>
+        <v>2.255019504430016</v>
       </c>
       <c r="N6" t="n">
-        <v>7.536366116232895</v>
+        <v>7.537486911998573</v>
       </c>
       <c r="O6" t="n">
-        <v>2.745244272598141</v>
+        <v>2.745448399077749</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9119265628481</v>
+        <v>216.9352506829575</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37906,7 +38054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G976"/>
+  <dimension ref="A1:G980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74021,6 +74169,154 @@
         </is>
       </c>
     </row>
+    <row r="977">
+      <c r="A977" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-25 22:07:19+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>-41.042892531161584,173.02020746295227</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>-41.04241477932968,173.01943743451915</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>-41.04182716301736,173.0190323994084</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>-41.04119524141966,173.01855565038161</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>-41.04052476896904,173.0182068050762</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>-41.04288948823714,173.02021350636852</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>-41.042416824546855,173.01943337255608</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>-41.04182766409377,173.01903074196875</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>-41.04119691309554,173.01855012638535</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>-41.0405267070446,173.01820039674155</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:07:14+00:00</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>-41.04290156016506,173.02018953084513</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>-41.04242211218079,173.01942287089426</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>-41.041831405463576,173.01901836641858</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>-41.0412001227125,173.01853952031178</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>-41.040530215628735,173.0181887954451</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>-41.04292006711923,173.02015277496375</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>-41.042422461364126,173.01942217738824</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>-41.041831438868655,173.01901825592262</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>-41.04120025644654,173.01853907839202</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>-41.04053024904381,173.01818868495658</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G980"/>
+  <dimension ref="A1:G984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26896,6 +26896,114 @@
         <v>220.11</v>
       </c>
       <c r="G980" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>244.95</v>
+      </c>
+      <c r="C981" t="n">
+        <v>223.51</v>
+      </c>
+      <c r="D981" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="E981" t="n">
+        <v>219.47</v>
+      </c>
+      <c r="F981" t="n">
+        <v>220.09</v>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>244.95</v>
+      </c>
+      <c r="C982" t="n">
+        <v>223.79</v>
+      </c>
+      <c r="D982" t="n">
+        <v>231.03</v>
+      </c>
+      <c r="E982" t="n">
+        <v>219.59</v>
+      </c>
+      <c r="F982" t="n">
+        <v>220.76</v>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>249.85</v>
+      </c>
+      <c r="C983" t="n">
+        <v>223.68</v>
+      </c>
+      <c r="D983" t="n">
+        <v>230.99</v>
+      </c>
+      <c r="E983" t="n">
+        <v>220.01</v>
+      </c>
+      <c r="F983" t="n">
+        <v>221.33</v>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>257.63</v>
+      </c>
+      <c r="C984" t="n">
+        <v>224.24</v>
+      </c>
+      <c r="D984" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="E984" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="F984" t="n">
+        <v>221.44</v>
+      </c>
+      <c r="G984" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26912,7 +27020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1063"/>
+  <dimension ref="A1:B1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37545,6 +37653,46 @@
       </c>
       <c r="B1063" t="n">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -37707,28 +37855,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5869226719078113</v>
+        <v>0.5869224990029854</v>
       </c>
       <c r="J2" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="K2" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09219321485729204</v>
+        <v>0.09292873970323645</v>
       </c>
       <c r="M2" t="n">
-        <v>9.848775466821383</v>
+        <v>9.826533634627042</v>
       </c>
       <c r="N2" t="n">
-        <v>189.1664720566333</v>
+        <v>188.5057171512888</v>
       </c>
       <c r="O2" t="n">
-        <v>13.75378028240357</v>
+        <v>13.729738422537</v>
       </c>
       <c r="P2" t="n">
-        <v>233.6874346327299</v>
+        <v>233.6874018486972</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37779,28 +37927,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04367660491374936</v>
+        <v>0.04254905827745038</v>
       </c>
       <c r="J3" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="K3" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01523726994646768</v>
+        <v>0.01458911527421836</v>
       </c>
       <c r="M3" t="n">
-        <v>2.236267136486437</v>
+        <v>2.232833641248762</v>
       </c>
       <c r="N3" t="n">
-        <v>6.875592259739072</v>
+        <v>6.855512939482675</v>
       </c>
       <c r="O3" t="n">
-        <v>2.622135057494002</v>
+        <v>2.618303446791963</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0150062607071</v>
+        <v>224.0267717686121</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37851,28 +37999,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1303973920187286</v>
+        <v>0.1302337513538865</v>
       </c>
       <c r="J4" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="K4" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1466754379547395</v>
+        <v>0.1475273013180602</v>
       </c>
       <c r="M4" t="n">
-        <v>1.987150821290527</v>
+        <v>1.979814800192956</v>
       </c>
       <c r="N4" t="n">
-        <v>5.516740951029801</v>
+        <v>5.494482984668393</v>
       </c>
       <c r="O4" t="n">
-        <v>2.348774350811461</v>
+        <v>2.344031353175207</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7707783374848</v>
+        <v>227.7724855987008</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37923,28 +38071,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1144774580889094</v>
+        <v>0.1128104318012513</v>
       </c>
       <c r="J5" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="K5" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07570282387871829</v>
+        <v>0.07418145420115352</v>
       </c>
       <c r="M5" t="n">
-        <v>2.459200352490003</v>
+        <v>2.456950781344644</v>
       </c>
       <c r="N5" t="n">
-        <v>8.923339753069115</v>
+        <v>8.904318939096132</v>
       </c>
       <c r="O5" t="n">
-        <v>2.98719596830692</v>
+        <v>2.98401054607656</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8725072544698</v>
+        <v>218.8899016329813</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37995,28 +38143,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2457185611822711</v>
+        <v>0.243598470951128</v>
       </c>
       <c r="J6" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="K6" t="n">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3087821704936267</v>
+        <v>0.3062858167096723</v>
       </c>
       <c r="M6" t="n">
-        <v>2.255019504430016</v>
+        <v>2.255938312637038</v>
       </c>
       <c r="N6" t="n">
-        <v>7.537486911998573</v>
+        <v>7.534847280254407</v>
       </c>
       <c r="O6" t="n">
-        <v>2.745448399077749</v>
+        <v>2.744967628270761</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9352506829575</v>
+        <v>216.9573729550345</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38054,7 +38202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G980"/>
+  <dimension ref="A1:G984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74317,6 +74465,154 @@
         </is>
       </c>
     </row>
+    <row r="981">
+      <c r="A981" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>-41.042917772457095,173.02015733229786</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>-41.042424606347396,173.0194179172796</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>-41.04183237421089,173.01901516203483</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>-41.04120156035311,173.01853476967432</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>-41.04053031587397,173.01818846397947</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>-41.042917772457095,173.02015733229786</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>-41.04242320961412,173.01942069130385</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>-41.04183220718551,173.0190157145148</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>-41.041201159151115,173.01853609543363</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>-41.04052807706331,173.01819586671166</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:25+00:00</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>-41.04289332930566,173.02020587779384</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>-41.04242375833078,173.01941960150864</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>-41.04183234080582,173.01901527253085</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>-41.04119975494394,173.01854073559107</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>-41.04052617240311,173.01820216455803</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:09+00:00</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>-41.042854519525015,173.02028295607897</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>-41.042420964864064,173.01942514955687</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>-41.04183163929914,173.01901759294668</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>-41.041198083268505,173.01854625958782</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>-41.04052580483706,173.01820337993186</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G984"/>
+  <dimension ref="A1:G990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26962,7 +26962,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>249.85</v>
+        <v>244.67</v>
       </c>
       <c r="C983" t="n">
         <v>223.68</v>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>257.63</v>
+        <v>245.45</v>
       </c>
       <c r="C984" t="n">
         <v>224.24</v>
@@ -27004,6 +27004,168 @@
         <v>221.44</v>
       </c>
       <c r="G984" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>244.48</v>
+      </c>
+      <c r="C985" t="n">
+        <v>223.87</v>
+      </c>
+      <c r="D985" t="n">
+        <v>230.66</v>
+      </c>
+      <c r="E985" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="F985" t="n">
+        <v>221.08</v>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>244.66</v>
+      </c>
+      <c r="C986" t="n">
+        <v>224.19</v>
+      </c>
+      <c r="D986" t="n">
+        <v>230.93</v>
+      </c>
+      <c r="E986" t="n">
+        <v>219.97</v>
+      </c>
+      <c r="F986" t="n">
+        <v>221.62</v>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>243.33</v>
+      </c>
+      <c r="C987" t="n">
+        <v>224.73</v>
+      </c>
+      <c r="D987" t="n">
+        <v>231.35</v>
+      </c>
+      <c r="E987" t="n">
+        <v>220.72</v>
+      </c>
+      <c r="F987" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>242.57</v>
+      </c>
+      <c r="C988" t="n">
+        <v>224.78</v>
+      </c>
+      <c r="D988" t="n">
+        <v>231.33</v>
+      </c>
+      <c r="E988" t="n">
+        <v>220.66</v>
+      </c>
+      <c r="F988" t="n">
+        <v>222.49</v>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>249.66</v>
+      </c>
+      <c r="C989" t="n">
+        <v>224.87</v>
+      </c>
+      <c r="D989" t="n">
+        <v>231.31</v>
+      </c>
+      <c r="E989" t="n">
+        <v>220.57</v>
+      </c>
+      <c r="F989" t="n">
+        <v>222.7</v>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>254.16</v>
+      </c>
+      <c r="C990" t="n">
+        <v>225.26</v>
+      </c>
+      <c r="D990" t="n">
+        <v>231.52</v>
+      </c>
+      <c r="E990" t="n">
+        <v>220.99</v>
+      </c>
+      <c r="F990" t="n">
+        <v>223.29</v>
+      </c>
+      <c r="G990" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27020,7 +27182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1067"/>
+  <dimension ref="A1:B1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37693,6 +37855,66 @@
       </c>
       <c r="B1067" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -37855,28 +38077,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5869224990029854</v>
+        <v>0.5798899151443628</v>
       </c>
       <c r="J2" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="K2" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09292873970323645</v>
+        <v>0.09201849018309582</v>
       </c>
       <c r="M2" t="n">
-        <v>9.826533634627042</v>
+        <v>9.776379433035004</v>
       </c>
       <c r="N2" t="n">
-        <v>188.5057171512888</v>
+        <v>187.4805321290263</v>
       </c>
       <c r="O2" t="n">
-        <v>13.729738422537</v>
+        <v>13.69235305303753</v>
       </c>
       <c r="P2" t="n">
-        <v>233.6874018486972</v>
+        <v>233.7609095763385</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37927,28 +38149,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04254905827745038</v>
+        <v>0.04188365830827587</v>
       </c>
       <c r="J3" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="K3" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01458911527421836</v>
+        <v>0.01433146647608752</v>
       </c>
       <c r="M3" t="n">
-        <v>2.232833641248762</v>
+        <v>2.222842699253667</v>
       </c>
       <c r="N3" t="n">
-        <v>6.855512939482675</v>
+        <v>6.816989736520449</v>
       </c>
       <c r="O3" t="n">
-        <v>2.618303446791963</v>
+        <v>2.610936563097704</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0267717686121</v>
+        <v>224.0337330321854</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37999,28 +38221,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1302337513538865</v>
+        <v>0.1301436478969885</v>
       </c>
       <c r="J4" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="K4" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1475273013180602</v>
+        <v>0.1490949443500091</v>
       </c>
       <c r="M4" t="n">
-        <v>1.979814800192956</v>
+        <v>1.969173037274835</v>
       </c>
       <c r="N4" t="n">
-        <v>5.494482984668393</v>
+        <v>5.461693218961788</v>
       </c>
       <c r="O4" t="n">
-        <v>2.344031353175207</v>
+        <v>2.337026576434635</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7724855987008</v>
+        <v>227.7734256045261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38071,28 +38293,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1128104318012513</v>
+        <v>0.1109363362901476</v>
       </c>
       <c r="J5" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="K5" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07418145420115352</v>
+        <v>0.07272267511706731</v>
       </c>
       <c r="M5" t="n">
-        <v>2.456950781344644</v>
+        <v>2.450684326896445</v>
       </c>
       <c r="N5" t="n">
-        <v>8.904318939096132</v>
+        <v>8.866466877322292</v>
       </c>
       <c r="O5" t="n">
-        <v>2.98401054607656</v>
+        <v>2.97766131004221</v>
       </c>
       <c r="P5" t="n">
-        <v>218.8899016329813</v>
+        <v>218.9095178392736</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38143,28 +38365,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.243598470951128</v>
+        <v>0.2421044397667727</v>
       </c>
       <c r="J6" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="K6" t="n">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3062858167096723</v>
+        <v>0.3062798701336292</v>
       </c>
       <c r="M6" t="n">
-        <v>2.255938312637038</v>
+        <v>2.249329319655196</v>
       </c>
       <c r="N6" t="n">
-        <v>7.534847280254407</v>
+        <v>7.501265098812343</v>
       </c>
       <c r="O6" t="n">
-        <v>2.744967628270761</v>
+        <v>2.738843752172136</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9573729550345</v>
+        <v>216.9730070609287</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38202,7 +38424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G984"/>
+  <dimension ref="A1:G990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74547,7 +74769,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>-41.04289332930566,173.02020587779384</t>
+          <t>-41.042919169208,173.02015455826844</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
@@ -74584,7 +74806,7 @@
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>-41.042854519525015,173.02028295607897</t>
+          <t>-41.04291527825892,173.02016228592154</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
@@ -74608,6 +74830,228 @@
         </is>
       </c>
       <c r="G984" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>-41.0429201170032,173.02015267589124</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>-41.04242281054746,173.01942148388218</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>-41.04183344317336,173.019011626163</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>-41.0412021955896,173.01853267055537</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>-41.04052700778041,173.01819940234478</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>-41.042919219091964,173.02015445919594</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>-41.04242121428075,173.01942465419543</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>-41.04183254123628,173.0190146095549</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>-41.041199888677966,173.01854029367132</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>-41.04052520336532,173.01820536872538</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:02+00:00</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>-41.042925853657756,173.02014128255456</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>-41.04241852058048,173.01943000409867</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>-41.04183113822292,173.01901925038652</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>-41.04119738116475,173.01854857966634</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>-41.04052293113846,173.01821288194492</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:11+00:00</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>-41.04292964483755,173.020133753044</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>-41.042418271163776,173.01943049946007</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>-41.041831205033084,173.0190190293945</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>-41.04119758176583,173.0185479167868</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>-41.04052229625146,173.01821498122675</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>-41.0428942771017,173.02020399541814</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>-41.04241782221369,173.01943139111057</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>-41.04183127184325,173.01901880840256</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>-41.04119788266744,173.0185469224674</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>-41.0405215945342,173.01821730148558</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>-41.042871829292196,173.02024857798614</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>-41.0424158767633,173.01943525492922</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>-41.0418305703365,173.01902112881828</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>-41.041196478459845,173.01855156262442</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>-41.04051962304259,173.01822382030775</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G990"/>
+  <dimension ref="A1:G994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27124,7 +27124,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>249.66</v>
+        <v>242.57</v>
       </c>
       <c r="C989" t="n">
         <v>224.87</v>
@@ -27151,7 +27151,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>254.16</v>
+        <v>242.45</v>
       </c>
       <c r="C990" t="n">
         <v>225.26</v>
@@ -27168,6 +27168,114 @@
       <c r="G990" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>243.23</v>
+      </c>
+      <c r="C991" t="n">
+        <v>225.69</v>
+      </c>
+      <c r="D991" t="n">
+        <v>231.7</v>
+      </c>
+      <c r="E991" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="F991" t="n">
+        <v>223.66</v>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>243.23</v>
+      </c>
+      <c r="C992" t="n">
+        <v>225.93</v>
+      </c>
+      <c r="D992" t="n">
+        <v>232.02</v>
+      </c>
+      <c r="E992" t="n">
+        <v>221.82</v>
+      </c>
+      <c r="F992" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>246.44</v>
+      </c>
+      <c r="C993" t="n">
+        <v>225.96</v>
+      </c>
+      <c r="D993" t="n">
+        <v>231.8</v>
+      </c>
+      <c r="E993" t="n">
+        <v>222.09</v>
+      </c>
+      <c r="F993" t="n">
+        <v>224.93</v>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>246.44</v>
+      </c>
+      <c r="C994" t="n">
+        <v>226.21</v>
+      </c>
+      <c r="D994" t="n">
+        <v>232.04</v>
+      </c>
+      <c r="E994" t="n">
+        <v>222.48</v>
+      </c>
+      <c r="F994" t="n">
+        <v>225.29</v>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27182,7 +27290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1073"/>
+  <dimension ref="A1:B1077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37915,6 +38023,46 @@
       </c>
       <c r="B1073" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>1.81</v>
       </c>
     </row>
   </sheetData>
@@ -38077,28 +38225,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5798899151443628</v>
+        <v>0.5725155756132801</v>
       </c>
       <c r="J2" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="K2" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09201849018309582</v>
+        <v>0.09058747662994293</v>
       </c>
       <c r="M2" t="n">
-        <v>9.776379433035004</v>
+        <v>9.743924264686646</v>
       </c>
       <c r="N2" t="n">
-        <v>187.4805321290263</v>
+        <v>186.8816752452915</v>
       </c>
       <c r="O2" t="n">
-        <v>13.69235305303753</v>
+        <v>13.67046726506784</v>
       </c>
       <c r="P2" t="n">
-        <v>233.7609095763385</v>
+        <v>233.8382792540912</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38149,28 +38297,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04188365830827587</v>
+        <v>0.04251715061803962</v>
       </c>
       <c r="J3" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="K3" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01433146647608752</v>
+        <v>0.01489039597689246</v>
       </c>
       <c r="M3" t="n">
-        <v>2.222842699253667</v>
+        <v>2.21699671909519</v>
       </c>
       <c r="N3" t="n">
-        <v>6.816989736520449</v>
+        <v>6.792129331175933</v>
       </c>
       <c r="O3" t="n">
-        <v>2.610936563097704</v>
+        <v>2.60617139328478</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0337330321854</v>
+        <v>224.0270780852087</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38221,28 +38369,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1301436478969885</v>
+        <v>0.1306442429841263</v>
       </c>
       <c r="J4" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="K4" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1490949443500091</v>
+        <v>0.1512087225554078</v>
       </c>
       <c r="M4" t="n">
-        <v>1.969173037274835</v>
+        <v>1.963889379818943</v>
       </c>
       <c r="N4" t="n">
-        <v>5.461693218961788</v>
+        <v>5.441316081773092</v>
       </c>
       <c r="O4" t="n">
-        <v>2.337026576434635</v>
+        <v>2.33266287357884</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7734256045261</v>
+        <v>227.7681671799725</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38293,28 +38441,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1109363362901476</v>
+        <v>0.11093166914098</v>
       </c>
       <c r="J5" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="K5" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07272267511706731</v>
+        <v>0.07333153920196978</v>
       </c>
       <c r="M5" t="n">
-        <v>2.450684326896445</v>
+        <v>2.44241713091126</v>
       </c>
       <c r="N5" t="n">
-        <v>8.866466877322292</v>
+        <v>8.831694018676805</v>
       </c>
       <c r="O5" t="n">
-        <v>2.97766131004221</v>
+        <v>2.971816619288075</v>
       </c>
       <c r="P5" t="n">
-        <v>218.9095178392736</v>
+        <v>218.9095639735169</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38365,28 +38513,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2421044397667727</v>
+        <v>0.242963564667206</v>
       </c>
       <c r="J6" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="K6" t="n">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3062798701336292</v>
+        <v>0.3095738653436512</v>
       </c>
       <c r="M6" t="n">
-        <v>2.249329319655196</v>
+        <v>2.244739543536936</v>
       </c>
       <c r="N6" t="n">
-        <v>7.501265098812343</v>
+        <v>7.477123802990402</v>
       </c>
       <c r="O6" t="n">
-        <v>2.738843752172136</v>
+        <v>2.734432994788938</v>
       </c>
       <c r="P6" t="n">
-        <v>216.9730070609287</v>
+        <v>216.963979430349</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38424,7 +38572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G990"/>
+  <dimension ref="A1:G994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74991,7 +75139,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>-41.0428942771017,173.02020399541814</t>
+          <t>-41.04292964483755,173.020133753044</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
@@ -75028,7 +75176,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>-41.042871829292196,173.02024857798614</t>
+          <t>-41.042930243444815,173.02013256417382</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
@@ -75054,6 +75202,154 @@
       <c r="G990" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:06+00:00</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>-41.04292635249722,173.02014029182953</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>-41.04241373177937,173.0194395150367</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>-41.04182996904496,173.01902311774606</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>-41.04119594352357,173.01855333030323</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>-41.04051838668326,173.01822790838247</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:06:41+00:00</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>-41.04292635249722,173.02014029182953</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>-41.04241253457898,173.01944189277103</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>-41.04182890008216,173.01902665361752</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>-41.04119370347761,173.01856073245793</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>-41.040516281530564,173.018234869158</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>-41.04291033974588,173.02017209409533</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>-41.04241238492892,173.01944218998779</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>-41.0418296349941,173.0190242227059</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>-41.0411928007724,173.01856371541564</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>-41.0405141429623,173.01824194042155</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>-41.04291033974588,173.02017209409533</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>-41.04241113784513,173.01944466679424</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>-41.04182883327198,173.01902687460947</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>-41.0411914968647,173.01856802413224</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>-41.040512940017464,173.0182459180071</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0577/nzd0577.xlsx
+++ b/data/nzd0577/nzd0577.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G994"/>
+  <dimension ref="A1:G998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27232,7 +27232,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>246.44</v>
+        <v>241.29</v>
       </c>
       <c r="C993" t="n">
         <v>225.96</v>
@@ -27259,7 +27259,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>246.44</v>
+        <v>241.29</v>
       </c>
       <c r="C994" t="n">
         <v>226.21</v>
@@ -27276,6 +27276,114 @@
       <c r="G994" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>240.35</v>
+      </c>
+      <c r="C995" t="n">
+        <v>226.64</v>
+      </c>
+      <c r="D995" t="n">
+        <v>232.05</v>
+      </c>
+      <c r="E995" t="n">
+        <v>222.96</v>
+      </c>
+      <c r="F995" t="n">
+        <v>225.64</v>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>242.71</v>
+      </c>
+      <c r="C996" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="D996" t="n">
+        <v>232.54</v>
+      </c>
+      <c r="E996" t="n">
+        <v>223.84</v>
+      </c>
+      <c r="F996" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>242.71</v>
+      </c>
+      <c r="C997" t="n">
+        <v>227.39</v>
+      </c>
+      <c r="D997" t="n">
+        <v>232.47</v>
+      </c>
+      <c r="E997" t="n">
+        <v>224.11</v>
+      </c>
+      <c r="F997" t="n">
+        <v>226</v>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>241.93</v>
+      </c>
+      <c r="C998" t="n">
+        <v>227.47</v>
+      </c>
+      <c r="D998" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="E998" t="n">
+        <v>224.23</v>
+      </c>
+      <c r="F998" t="n">
+        <v>225.88</v>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27290,7 +27398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1077"/>
+  <dimension ref="A1:B1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38063,6 +38171,46 @@
       </c>
       <c r="B1077" t="n">
         <v>1.81</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -38225,28 +38373,28 @@
         <v>0.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5725155756132801</v>
+        <v>0.5646197296548079</v>
       </c>
       <c r="J2" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K2" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09058747662994293</v>
+        <v>0.08892348136410244</v>
       </c>
       <c r="M2" t="n">
-        <v>9.743924264686646</v>
+        <v>9.723410757781538</v>
       </c>
       <c r="N2" t="n">
-        <v>186.8816752452915</v>
+        <v>186.4565701076085</v>
       </c>
       <c r="O2" t="n">
-        <v>13.67046726506784</v>
+        <v>13.6549101098326</v>
       </c>
       <c r="P2" t="n">
-        <v>233.8382792540912</v>
+        <v>233.9214183331246</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38297,28 +38445,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04251715061803962</v>
+        <v>0.0441169725928417</v>
       </c>
       <c r="J3" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K3" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01489039597689246</v>
+        <v>0.01612036922308491</v>
       </c>
       <c r="M3" t="n">
-        <v>2.21699671909519</v>
+        <v>2.215945096474912</v>
       </c>
       <c r="N3" t="n">
-        <v>6.792129331175933</v>
+        <v>6.781184876495846</v>
       </c>
       <c r="O3" t="n">
-        <v>2.60617139328478</v>
+        <v>2.604070827857001</v>
       </c>
       <c r="P3" t="n">
-        <v>224.0270780852087</v>
+        <v>224.0102189253884</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38369,28 +38517,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1306442429841263</v>
+        <v>0.1315269298913877</v>
       </c>
       <c r="J4" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K4" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1512087225554078</v>
+        <v>0.1540145347169739</v>
       </c>
       <c r="M4" t="n">
-        <v>1.963889379818943</v>
+        <v>1.960650039988046</v>
       </c>
       <c r="N4" t="n">
-        <v>5.441316081773092</v>
+        <v>5.424475527303804</v>
       </c>
       <c r="O4" t="n">
-        <v>2.33266287357884</v>
+        <v>2.329050348812538</v>
       </c>
       <c r="P4" t="n">
-        <v>227.7681671799725</v>
+        <v>227.7588653647988</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38441,28 +38589,28 @@
         <v>0.1768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.11093166914098</v>
+        <v>0.1124417518643349</v>
       </c>
       <c r="J5" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K5" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07333153920196978</v>
+        <v>0.07570875536265897</v>
       </c>
       <c r="M5" t="n">
-        <v>2.44241713091126</v>
+        <v>2.440682938384052</v>
       </c>
       <c r="N5" t="n">
-        <v>8.831694018676805</v>
+        <v>8.811404415117785</v>
       </c>
       <c r="O5" t="n">
-        <v>2.971816619288075</v>
+        <v>2.96840098624121</v>
       </c>
       <c r="P5" t="n">
-        <v>218.9095639735169</v>
+        <v>218.8936492632508</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38513,28 +38661,28 @@
         <v>0.1821</v>
       </c>
       <c r="I6" t="n">
-        <v>0.242963564667206</v>
+        <v>0.2449004270726273</v>
       </c>
       <c r="J6" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="K6" t="n">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3095738653436512</v>
+        <v>0.3142710420680769</v>
       </c>
       <c r="M6" t="n">
-        <v>2.244739543536936</v>
+        <v>2.245768736575076</v>
       </c>
       <c r="N6" t="n">
-        <v>7.477123802990402</v>
+        <v>7.470581434227245</v>
       </c>
       <c r="O6" t="n">
-        <v>2.734432994788938</v>
+        <v>2.733236439503038</v>
       </c>
       <c r="P6" t="n">
-        <v>216.963979430349</v>
+        <v>216.9435703903134</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38572,7 +38720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G994"/>
+  <dimension ref="A1:G998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75287,7 +75435,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>-41.04291033974588,173.02017209409533</t>
+          <t>-41.042936029981306,173.02012107176108</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
@@ -75324,7 +75472,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>-41.04291033974588,173.02017209409533</t>
+          <t>-41.042936029981306,173.02012107176108</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
@@ -75350,6 +75498,154 @@
       <c r="G994" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>-41.04294071907038,173.0201117589424</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>-41.04240899286086,173.0194489269011</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>-41.04182879986689,173.01902698510546</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>-41.04118989205504,173.01857332716776</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>-41.04051177048763,173.01824978510402</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:06:19+00:00</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>-41.04292894646235,173.02013514005915</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>-41.04240619939273,173.01945447494685</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>-41.04182716301736,173.0190323994084</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>-41.04118694990335,173.01858304939893</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>-41.04050989923962,173.0182559724588</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>-41.04292894646235,173.02013514005915</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>-41.042405251608834,173.01945635731943</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>-41.04182739685302,173.01903162593655</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>-41.041186047197534,173.018586032356</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>-41.040510567542526,173.01825376268928</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:30+00:00</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>-41.0429328374096,173.02012741240284</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>-41.04240485254193,173.01945714989733</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>-41.04182729663774,173.0190319574245</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>-41.041185645994936,173.01858735811473</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>-41.04051096852423,173.01825243682754</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
